--- a/deliverables/tools/Application_Command_Center.xlsx
+++ b/deliverables/tools/Application_Command_Center.xlsx
@@ -724,7 +724,7 @@
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -741,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>What this is</t>
@@ -760,7 +760,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="62" customHeight="1">
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Tracker</t>
@@ -772,7 +772,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="62" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Funding Matrix</t>
@@ -784,7 +784,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="62" customHeight="1">
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Documents</t>
@@ -796,7 +796,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="62" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>All Programs</t>
@@ -808,7 +808,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="56" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>How the dropdowns work</t>
